--- a/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
@@ -807,15 +807,19 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1056,15 +1060,19 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1305,15 +1313,19 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1554,15 +1566,19 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1803,15 +1819,19 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2052,15 +2072,19 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr"/>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2301,15 +2325,19 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2550,15 +2578,19 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr"/>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2799,15 +2831,19 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3048,15 +3084,19 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr"/>
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3297,15 +3337,19 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3546,15 +3590,19 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3795,15 +3843,19 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4044,15 +4096,19 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4293,15 +4349,19 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4542,15 +4602,19 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4791,15 +4855,19 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr"/>
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5040,15 +5108,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5289,15 +5361,19 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5538,15 +5614,19 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5787,15 +5867,19 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6036,15 +6120,19 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6285,15 +6373,19 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6534,15 +6626,19 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6783,15 +6879,19 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr"/>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7032,15 +7132,19 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7281,15 +7385,19 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr"/>
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7530,15 +7638,19 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr"/>
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7779,15 +7891,19 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr"/>
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8028,15 +8144,19 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8261,15 +8381,19 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8510,15 +8634,19 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr"/>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>TRATADO</t>
+        </is>
+      </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>111001047017</t>
+          <t>111001098817</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ATABANZHA</t>
+          <t>COLEGIO NUEVA ROMA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
@@ -809,17 +809,17 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1315,17 +1315,17 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1568,17 +1568,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1821,17 +1821,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2074,17 +2074,17 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2327,17 +2327,17 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2580,17 +2580,17 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3086,17 +3086,17 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3339,17 +3339,17 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3592,17 +3592,17 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3845,17 +3845,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4098,17 +4098,17 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4351,17 +4351,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4604,17 +4604,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4857,17 +4857,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5110,17 +5110,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5363,17 +5363,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5616,17 +5616,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5869,17 +5869,17 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6122,17 +6122,17 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6375,17 +6375,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6628,17 +6628,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6881,17 +6881,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7134,17 +7134,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7387,17 +7387,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7640,17 +7640,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7893,17 +7893,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8146,17 +8146,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8383,17 +8383,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8636,17 +8636,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TRATADO</t>
+          <t>CONTROL</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>111001098817</t>
+          <t>111001046931</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO NUEVA ROMA (IED)</t>
+          <t>COLEGIO ATABANZHA (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO ATABANZA DIAGNOSTICA 703_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3590,11 +3546,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -3602,7 +3554,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3843,11 +3795,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -3855,7 +3803,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4096,11 +4044,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -4108,7 +4052,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4349,11 +4293,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -4361,7 +4301,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4602,11 +4542,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -4614,7 +4550,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4855,11 +4791,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -4867,7 +4799,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5108,11 +5040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -5120,7 +5048,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5361,11 +5289,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -5373,7 +5297,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5614,11 +5538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -5626,7 +5546,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5867,11 +5787,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -5879,7 +5795,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6120,11 +6036,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -6132,7 +6044,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6373,11 +6285,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -6385,7 +6293,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6626,11 +6534,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -6638,7 +6542,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6879,11 +6783,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -6891,7 +6791,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7132,11 +7032,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -7144,7 +7040,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7385,11 +7281,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -7397,7 +7289,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7638,11 +7530,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -7650,7 +7538,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7891,11 +7779,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -7903,7 +7787,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8144,11 +8028,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -8156,7 +8036,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8381,11 +8261,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -8393,7 +8269,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8634,11 +8510,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001046931</t>
@@ -8646,7 +8518,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO ATABANZHA (IED)</t>
+          <t>ATABANZHA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
